--- a/Wednesday_Class_Timetable.xlsx
+++ b/Wednesday_Class_Timetable.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>MATHS (RABIA IQBAL)</t>
+          <t>GAMES (NAZAR ABBASS)</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
